--- a/Assets/StreamingAssets/Text.xlsx
+++ b/Assets/StreamingAssets/Text.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView windowWidth="24750" windowHeight="11480"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
   <si>
     <t>ID</t>
   </si>
@@ -51,6 +51,12 @@
   </si>
   <si>
     <t>nextID_notAnswered</t>
+  </si>
+  <si>
+    <t>playtime</t>
+  </si>
+  <si>
+    <t>isAutoPlay</t>
   </si>
   <si>
     <t>Narrator</t>
@@ -1023,19 +1029,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="7"/>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6"/>
   <cols>
     <col min="2" max="2" width="15.4166666666667" customWidth="1"/>
     <col min="3" max="3" width="54.25" customWidth="1"/>
     <col min="4" max="4" width="9.25" customWidth="1"/>
     <col min="5" max="5" width="12.0833333333333" customWidth="1"/>
     <col min="6" max="6" width="10.8333333333333" customWidth="1"/>
-    <col min="7" max="8" width="12.75" customWidth="1"/>
+    <col min="7" max="7" width="12.75" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
     <col min="9" max="10" width="11.1666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1060,16 +1067,22 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:10">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1077,16 +1090,22 @@
       <c r="E2" t="b">
         <v>0</v>
       </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:10">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1094,16 +1113,22 @@
       <c r="E3" t="b">
         <v>0</v>
       </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:10">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1111,16 +1136,22 @@
       <c r="E4" t="b">
         <v>0</v>
       </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:10">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1128,16 +1159,22 @@
       <c r="E5" t="b">
         <v>0</v>
       </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:10">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1145,22 +1182,34 @@
       <c r="E6" t="b">
         <v>0</v>
       </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:10">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D7">
         <v>6</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
